--- a/docs/places.xlsx
+++ b/docs/places.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mdomind/Documents/Anniv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3E6EDD-528B-C145-A826-C3BBB8DCE8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F234288A-5CDC-3C47-BB6F-8BCC6D794B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1000" yWindow="760" windowWidth="28400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="how to use" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">places!$A$1:$J$399</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">places!$A$1:$J$398</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
   <si>
     <t>name</t>
   </si>
@@ -345,9 +345,6 @@
     <t>Barcelona</t>
   </si>
   <si>
-    <t>Así pues empezamos a salir y nos empezamos a interesar aún más en el otro. Me enseñaste a hacer ganchillo en tu casa, yo ten enseñé mis pannekoeken estrella de desayuno, buscabamos satelites en las noches juntos. Y así, poco a poco, cada vez queríamos salir menos de la casa de la otra persona.</t>
-  </si>
-  <si>
     <t>Limburg</t>
   </si>
   <si>
@@ -522,7 +519,88 @@
     <t>Hasta pronto</t>
   </si>
   <si>
-    <t>Conociendo a Saint Jordi y a los suegros</t>
+    <t>Así pues, empezamos a salir y nos empezamos a interesar aún más en el otro. Me enseñaste a hacer ganchillo en tu casa, yo ten enseñé mis pannekoeken estrella de desayuno, buscabamos satelites en las noches juntos. Y así, poco a poco, cada vez queríamos salir menos de la casa de la otra persona.</t>
+  </si>
+  <si>
+    <t>Seguimos conociendonos más y te empezaste a unir a mis rodadas. Te llevé al famoso Mossel, mientras you were rocking el maillot y el coulotte de ciclismo</t>
+  </si>
+  <si>
+    <t>Tuvimos nuestra primera escapada romántica y nos fuimos al sur (Siempre al sur). En un pequeño bosque increible caminamos, comimos rico y celebramos, como siempre, estar juntos.</t>
+  </si>
+  <si>
+    <t>Poco después de conocerla, la nini consiguió trabajo y entonces se convirtió instantanemaente en mi filósofa favorita.</t>
+  </si>
+  <si>
+    <t>Y después de decirs que estabamos dating faltaba la pieza para completar el rompecabezas: Una cita de verdad! Nos escapamos a Arnhem en donde sin querer queriendo terminamos teniendo nuestra cita a tan solo unas cuadras de donde terminaríamos viviendo.</t>
+  </si>
+  <si>
+    <t>Una vez más llegó la distancia y en las vacaciones cada uno partió en diferentes rumbos, pero eso si, manteniendo el contacto constante.  Llamadas desde España, Portugal, Escocia, Italia, Holanda hasta que por fin ya no más llamadas…</t>
+  </si>
+  <si>
+    <t>Llegué de regreso a Holanda y alguien estaba ahí para recibirme! *Mi Noviaaa!* con una sorpresita hermosa y un sinfín de posibilidades juntos. Asi fue como empezó oficialmente nuestro noviazgo.</t>
+  </si>
+  <si>
+    <t>Y que mejor manera para celebrar que vlviendo a donde todo empezó? Volvimos a hacer el Veluweloop tu corriendo como una diosa, yo en la bici y caminando :/.</t>
+  </si>
+  <si>
+    <t>Oter@s!</t>
+  </si>
+  <si>
+    <t>Wageningen</t>
+  </si>
+  <si>
+    <t>oteros.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empezó también a crecear así nuestra amistad con Gala y Alberto y el inmenso fanatismo por OT. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">De repentch Arnehm nos empieza a coquetear de nuevo! Primero dandonos nuestra primera cita y ahora nos invitan a vivir por unas semanas en la gran ciudad! </t>
+  </si>
+  <si>
+    <t>Llega tu cumple 25 y nos vamos de paseo! Un paseo lleno de aventuras! Búsqueda de fósiles, comidas exóticas y todo en Gothague city con los amigüitos</t>
+  </si>
+  <si>
+    <t>Luego de un invierno a distancia Carlangas pega el gran salto al charco. Llega a Colombia!! Y que bien que nos la pasamos, realmente disfruttando del buen vivir! Rica comida, visitas al jardín botánico, conocer el paraiso en el que mi abuela se enamoró, cocinar paellita juntos, explorar los increibles bosques de remansos y por supuesto las calles de Cali llenas de Salsa!</t>
+  </si>
+  <si>
+    <t>Dif´cil de competir con todo lo increible de Cali nos fuimos para el eje cafetero, esta vez si solitos pa disfrutarnos aún más. Y qué nos encontramos? El  Spa más increible en la mitad de la selva1! Rios termales, jacuzzis privados, pájaros de todos los colores. El verde del bosque nos recarga para seguir con la aventura</t>
+  </si>
+  <si>
+    <t>Continuamos la aventura con unos bellos días en Santa Marta con la triste noticia de que el Tayrona no estaba abierto. Lástima, tocará volver. Sin embargo, nos disfrutamos cada día de sol y playa en las hermosas playas de Santa Marta y tu favorita Playa grande en Taganga.</t>
+  </si>
+  <si>
+    <t>Y nos fuimos también de paseo express a la hermosa ciudad de Cartagena, en donde España y Colombia se unen. Caminamos por sus hermosas calles de la ciudad amurallada bajo un calor increible. Esto si es el trópico, mi amor.</t>
+  </si>
+  <si>
+    <t>Llegó entonces el día de la boda de Pablo y Andrea. Y así fue como una posibilidad que pusimos en el libro se cumplió y pudimos celebrar una vez más juntos el amor. Bueno además de celebrar alguién se abalanzó por el ramo como sin no hubiera un mañana!</t>
+  </si>
+  <si>
+    <t>De regreso al viejo continente y rápidamente empezamos a planear otro paseito. Nos vamos pal Sur! O sorpresa jaja. Esta vez al sur de Alemania. Me enseñaste Lindau y en donde estuviste en tus intercambios, montamos bici dándole la vuelta al lago. What a dream!</t>
+  </si>
+  <si>
+    <t>Al regresar de Alemania nos esperaba una gran sorpresa. Nos mudamos juntos! Otra posibility que empezamos a hacer realidad. Conseguimos el apartamento soñado, en el centro, con mucho espacio y sobre todo, con una tina!! Buah que increible! Así, poquito a poquito empezamos a convertir el apartamento en nuestro hogar.</t>
+  </si>
+  <si>
+    <t>El orden de los factores no altera el producto… cierto? Después de mudarnos juntos por fin fuie a Barcelona a conocer a tu familia, y casi tan importante, a Sant Jordi!</t>
+  </si>
+  <si>
+    <t>Conociendo a Sant Jordi y a los suegros</t>
+  </si>
+  <si>
+    <t>Nuevo fichajes para el Brother James! Un Colombiano sin experiencia alguna, pero con buena actitud!</t>
+  </si>
+  <si>
+    <t>Empiezan nuestras micro aventuras en Arnhem! Una rodada al Veluwezoom y picnicsito en medio del bosque</t>
+  </si>
+  <si>
+    <t>De nuevo nos escapamos al sur y conozco tu hermosa montaña (Bueno, faltan los olivos, pero you get what I mean). Conozco también un poco más de ti y de dónde vienes, de tu padre y de tu abuelo, de tu madre y el pacharán, de misas en catala. Me gutas eh!</t>
+  </si>
+  <si>
+    <t>Voy a llevalte pa PR! Y nos fuimooos, o bueno lo trajimos a Arnhem! Bad Bunny en arhnem, que locura! Pero que buen concierto. Bailamos y cantamos mucho! Un Baile Inolvdable!</t>
+  </si>
+  <si>
+    <t>Y se marchó y a su barco le llamó libertad! Nos despedimos de nuevo, pero solo por un tiempo, te fuiste con tu kit de primeros auxilios emocionales y yo me quedé aquí esperándote a que vuelvas a casita… ya pronto</t>
   </si>
 </sst>
 </file>
@@ -533,7 +611,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,6 +642,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -636,10 +722,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -697,8 +784,18 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -999,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M399"/>
+  <dimension ref="A1:M398"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.33203125" bestFit="1" customWidth="1"/>
@@ -1059,7 +1156,7 @@
         <v>5.6680380000000001</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>31</v>
@@ -1281,10 +1378,10 @@
         <v>5.6603160015706804</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
@@ -1294,7 +1391,7 @@
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>49</v>
       </c>
@@ -1302,12 +1399,14 @@
         <v>50</v>
       </c>
       <c r="C11" s="8">
-        <v>51.978526928986398</v>
+        <v>51.978478000000003</v>
       </c>
       <c r="D11" s="8">
-        <v>5.9054332169222601</v>
-      </c>
-      <c r="E11" s="7"/>
+        <v>5.9053344000000001</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="F11" s="7" t="s">
         <v>51</v>
       </c>
@@ -1319,22 +1418,24 @@
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="C12" s="8">
-        <v>52.062359220013903</v>
+        <v>52.059863200000002</v>
       </c>
       <c r="D12" s="8">
-        <v>5.7614508649830798</v>
-      </c>
-      <c r="E12" s="7"/>
+        <v>5.7530286999999998</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F12" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -1346,10 +1447,10 @@
     </row>
     <row r="13" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="8">
         <v>51.551522889140998</v>
@@ -1357,9 +1458,11 @@
       <c r="D13" s="8">
         <v>5.9998255701487802</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>118</v>
+      </c>
       <c r="F13" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -1369,12 +1472,12 @@
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>67</v>
       </c>
       <c r="C14" s="8">
         <v>51.987376971306603</v>
@@ -1382,9 +1485,11 @@
       <c r="D14" s="8">
         <v>5.66610809903964</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="F14" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -1394,12 +1499,12 @@
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
     </row>
-    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="17">
         <v>51.969386766831597</v>
@@ -1407,9 +1512,11 @@
       <c r="D15" s="17">
         <v>5.6668202352241304</v>
       </c>
-      <c r="E15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>121</v>
+      </c>
       <c r="F15" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -1419,12 +1526,12 @@
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
     </row>
-    <row r="16" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16" s="17">
         <v>51.9788776926327</v>
@@ -1432,9 +1539,11 @@
       <c r="D16" s="17">
         <v>5.6496691771098897</v>
       </c>
-      <c r="E16" s="9"/>
+      <c r="E16" s="9" t="s">
+        <v>122</v>
+      </c>
       <c r="F16" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1446,10 +1555,10 @@
     </row>
     <row r="17" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" s="8">
         <v>52.028852747056298</v>
@@ -1457,9 +1566,11 @@
       <c r="D17" s="8">
         <v>5.8713290622572796</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="F17" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -1469,22 +1580,24 @@
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
     </row>
-    <row r="18" spans="1:13" ht="64" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>72</v>
+    <row r="18" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="C18" s="17">
-        <v>51.980840852408001</v>
+        <v>51.969757700000002</v>
       </c>
       <c r="D18" s="17">
-        <v>5.9078987839015298</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9" t="s">
-        <v>93</v>
+        <v>5.6665333000000002</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>126</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -1494,22 +1607,24 @@
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C19" s="17">
-        <v>52.052948899999997</v>
+        <v>51.980840852408001</v>
       </c>
       <c r="D19" s="17">
-        <v>4.1850053999999997</v>
-      </c>
-      <c r="E19" s="9"/>
+        <v>5.9078987839015298</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>128</v>
+      </c>
       <c r="F19" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -1519,22 +1634,24 @@
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
     </row>
-    <row r="20" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="18">
-        <v>3.4505309905077999</v>
-      </c>
-      <c r="D20" s="18">
-        <v>-76.554605677465403</v>
-      </c>
-      <c r="E20" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="C20" s="17">
+        <v>52.052948899999997</v>
+      </c>
+      <c r="D20" s="17">
+        <v>4.1850053999999997</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>129</v>
+      </c>
       <c r="F20" s="9" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -1544,22 +1661,24 @@
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
     </row>
-    <row r="21" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C21" s="18">
-        <v>4.8480686999999998</v>
+        <v>3.4505309905077999</v>
       </c>
       <c r="D21" s="18">
-        <v>-75.533355700000001</v>
-      </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="7" t="s">
-        <v>102</v>
+        <v>-76.554605677465403</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -1569,22 +1688,24 @@
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
     </row>
-    <row r="22" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="11">
-        <v>11.1948442</v>
-      </c>
-      <c r="D22" s="11">
-        <v>-74.230815100000001</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="9" t="s">
-        <v>81</v>
+    <row r="22" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="18">
+        <v>4.8480686999999998</v>
+      </c>
+      <c r="D22" s="18">
+        <v>-75.533355700000001</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -1594,22 +1715,24 @@
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
     </row>
-    <row r="23" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="9" t="s">
+    <row r="23" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="11">
+        <v>11.2702951</v>
+      </c>
+      <c r="D23" s="11">
+        <v>-74.196332999999996</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="C23" s="21">
-        <v>10.4232449</v>
-      </c>
-      <c r="D23" s="21">
-        <v>-75.549357599999993</v>
-      </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="20" t="s">
-        <v>82</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -1621,20 +1744,22 @@
     </row>
     <row r="24" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C24" s="21">
-        <v>3.4952779999999999</v>
+        <v>10.4232449</v>
       </c>
       <c r="D24" s="21">
-        <v>-76.469040699999994</v>
-      </c>
-      <c r="E24" s="9"/>
+        <v>-75.549357599999993</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>133</v>
+      </c>
       <c r="F24" s="20" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -1644,22 +1769,24 @@
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="11">
-        <v>47.511461400000002</v>
-      </c>
-      <c r="D25" s="11">
-        <v>9.4355592000000001</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7" t="s">
-        <v>56</v>
+    <row r="25" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="21">
+        <v>3.4952779999999999</v>
+      </c>
+      <c r="D25" s="21">
+        <v>-76.469040699999994</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>102</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -1669,21 +1796,24 @@
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" ht="80" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="5">
-        <v>51.9803802989438</v>
-      </c>
-      <c r="D26" s="5">
-        <v>5.9054694152094998</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>112</v>
+    <row r="26" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="11">
+        <v>47.511461400000002</v>
+      </c>
+      <c r="D26" s="11">
+        <v>9.4355592000000001</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -1693,22 +1823,24 @@
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="11">
-        <v>41.444464037633097</v>
-      </c>
-      <c r="D27" s="11">
-        <v>2.0639060477991702</v>
-      </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7" t="s">
-        <v>105</v>
+    <row r="27" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="5">
+        <v>51.9803802989438</v>
+      </c>
+      <c r="D27" s="5">
+        <v>5.9054694152094998</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>111</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -1718,20 +1850,22 @@
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="22">
-        <v>41.4737467</v>
+        <v>138</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="11">
+        <v>41.444464037633097</v>
       </c>
       <c r="D28" s="11">
-        <v>2.3096339000000001</v>
-      </c>
-      <c r="E28" s="7"/>
+        <v>2.0639060477991702</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>137</v>
+      </c>
       <c r="F28" s="7" t="s">
         <v>104</v>
       </c>
@@ -1743,21 +1877,24 @@
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
-        <v>106</v>
+    <row r="29" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="5">
-        <v>52.022134200000004</v>
-      </c>
-      <c r="D29" s="5">
-        <v>5.9878369999999999</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>108</v>
+        <v>96</v>
+      </c>
+      <c r="C29" s="22">
+        <v>41.4737467</v>
+      </c>
+      <c r="D29" s="11">
+        <v>2.3096339000000001</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -1767,13 +1904,25 @@
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+    <row r="30" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="5">
+        <v>52.022134200000004</v>
+      </c>
+      <c r="D30" s="5">
+        <v>5.9878369999999999</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>107</v>
+      </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -1782,12 +1931,12 @@
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="64" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" s="11">
         <v>42.320655799999997</v>
@@ -1795,9 +1944,11 @@
       <c r="D31" s="11">
         <v>2.4811264999999998</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="E31" s="7" t="s">
+        <v>141</v>
+      </c>
       <c r="F31" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
@@ -1809,10 +1960,10 @@
     </row>
     <row r="32" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="C32" s="11">
         <v>51.962501500000002</v>
@@ -1820,24 +1971,26 @@
       <c r="D32" s="11">
         <v>5.8924998999999998</v>
       </c>
-      <c r="E32" s="7"/>
+      <c r="E32" s="7" t="s">
+        <v>142</v>
+      </c>
       <c r="F32" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
-      <c r="J32" s="16"/>
+      <c r="J32" s="7"/>
       <c r="K32" s="15"/>
       <c r="L32" s="15"/>
       <c r="M32" s="15"/>
     </row>
-    <row r="33" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" s="11">
         <v>52.308536699999998</v>
@@ -1845,14 +1998,16 @@
       <c r="D33" s="11">
         <v>4.7655200000000004</v>
       </c>
-      <c r="E33" s="7"/>
+      <c r="E33" s="7" t="s">
+        <v>143</v>
+      </c>
       <c r="F33" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
+        <v>113</v>
+      </c>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
       <c r="K33" s="15"/>
       <c r="L33" s="15"/>
       <c r="M33" s="15"/>
@@ -2473,19 +2628,8 @@
       <c r="M74" s="15"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A75" s="15"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
-      <c r="I75" s="15"/>
-      <c r="J75" s="15"/>
-      <c r="K75" s="15"/>
-      <c r="L75" s="15"/>
-      <c r="M75" s="15"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C76" s="12"/>
@@ -2524,8 +2668,8 @@
       <c r="D84" s="12"/>
     </row>
     <row r="85" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C85" s="12"/>
-      <c r="D85" s="12"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
     </row>
     <row r="86" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C86" s="1"/>
@@ -3779,19 +3923,18 @@
       <c r="C398" s="1"/>
       <c r="D398" s="1"/>
     </row>
-    <row r="399" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C399" s="1"/>
-      <c r="D399" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J399" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J398" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" promptTitle="pano" prompt="Put FALSE only where there is no Street View coverage." sqref="I2 I4:I6 I8:I400" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" promptTitle="pano" prompt="Put FALSE only where there is no Street View coverage." sqref="I2 I4:I6 I8:I399" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"FALSE"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A18" r:id="rId1" xr:uid="{729AE4E8-80F2-BD45-B4B5-9AF8D9163C84}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/docs/places.xlsx
+++ b/docs/places.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mdomind/Documents/Anniv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F234288A-5CDC-3C47-BB6F-8BCC6D794B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C6A101-55DE-4648-A0DA-41A6BCA5B8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1000" yWindow="760" windowWidth="28400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,9 +492,6 @@
     <t>Veluwezoom</t>
   </si>
   <si>
-    <t>veluwe_picnic.jpeg, veluew_picnic_2.jpeg , veluwe_picnic_2.jpeg</t>
-  </si>
-  <si>
     <t>Bad bunny!!</t>
   </si>
   <si>
@@ -601,6 +598,9 @@
   </si>
   <si>
     <t>Y se marchó y a su barco le llamó libertad! Nos despedimos de nuevo, pero solo por un tiempo, te fuiste con tu kit de primeros auxilios emocionales y yo me quedé aquí esperándote a que vuelvas a casita… ya pronto</t>
+  </si>
+  <si>
+    <t>veluwe_picnic.jpeg, veluew_picnic_1.jpeg , veluwe_picnic_2.jpeg</t>
   </si>
 </sst>
 </file>
@@ -726,7 +726,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -784,13 +784,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1378,7 +1372,7 @@
         <v>5.6603160015706804</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>61</v>
@@ -1405,7 +1399,7 @@
         <v>5.9053344000000001</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>51</v>
@@ -1432,7 +1426,7 @@
         <v>5.7530286999999998</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>88</v>
@@ -1459,7 +1453,7 @@
         <v>5.9998255701487802</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>60</v>
@@ -1486,7 +1480,7 @@
         <v>5.66610809903964</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>87</v>
@@ -1513,7 +1507,7 @@
         <v>5.6668202352241304</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>89</v>
@@ -1540,7 +1534,7 @@
         <v>5.6496691771098897</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>90</v>
@@ -1567,7 +1561,7 @@
         <v>5.8713290622572796</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>91</v>
@@ -1581,11 +1575,11 @@
       <c r="M17" s="15"/>
     </row>
     <row r="18" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="C18" s="17">
         <v>51.969757700000002</v>
@@ -1593,11 +1587,11 @@
       <c r="D18" s="17">
         <v>5.6665333000000002</v>
       </c>
-      <c r="E18" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="F18" s="25" t="s">
+      <c r="E18" s="9" t="s">
         <v>126</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>125</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -1621,7 +1615,7 @@
         <v>5.9078987839015298</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>92</v>
@@ -1648,7 +1642,7 @@
         <v>4.1850053999999997</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>93</v>
@@ -1675,7 +1669,7 @@
         <v>-76.554605677465403</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>86</v>
@@ -1702,7 +1696,7 @@
         <v>-75.533355700000001</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>101</v>
@@ -1729,7 +1723,7 @@
         <v>-74.196332999999996</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>80</v>
@@ -1756,7 +1750,7 @@
         <v>-75.549357599999993</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>81</v>
@@ -1783,7 +1777,7 @@
         <v>-76.469040699999994</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>102</v>
@@ -1810,7 +1804,7 @@
         <v>9.4355592000000001</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>56</v>
@@ -1836,11 +1830,11 @@
       <c r="D27" s="5">
         <v>5.9054694152094998</v>
       </c>
-      <c r="E27" s="23" t="s">
-        <v>136</v>
+      <c r="E27" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -1852,7 +1846,7 @@
     </row>
     <row r="28" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>57</v>
@@ -1864,7 +1858,7 @@
         <v>2.0639060477991702</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>104</v>
@@ -1891,7 +1885,7 @@
         <v>2.3096339000000001</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>103</v>
@@ -1917,11 +1911,11 @@
       <c r="D30" s="5">
         <v>5.9878369999999999</v>
       </c>
-      <c r="E30" s="23" t="s">
-        <v>140</v>
+      <c r="E30" s="9" t="s">
+        <v>139</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -1945,10 +1939,10 @@
         <v>2.4811264999999998</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
@@ -1960,10 +1954,10 @@
     </row>
     <row r="32" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>109</v>
       </c>
       <c r="C32" s="11">
         <v>51.962501500000002</v>
@@ -1972,10 +1966,10 @@
         <v>5.8924998999999998</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
@@ -1987,10 +1981,10 @@
     </row>
     <row r="33" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C33" s="11">
         <v>52.308536699999998</v>
@@ -1999,10 +1993,10 @@
         <v>4.7655200000000004</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15"/>
